--- a/training_schedule_updated.xlsx
+++ b/training_schedule_updated.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ron Tohar\Desktop\הכשרה\CV_training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43556C5C-0C27-4545-A825-360B78B72B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66D6A9F-6F43-411E-B7C4-8C663C531F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>Topic</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>estimated time</t>
+  </si>
+  <si>
+    <t>maybe 4.5 - 5</t>
   </si>
 </sst>
 </file>
@@ -451,12 +454,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -583,7 +587,7 @@
       </c>
       <c r="D12">
         <f>SUM(D13:D20)</f>
-        <v>8.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -630,7 +634,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>19</v>
       </c>
@@ -641,7 +645,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>20</v>
       </c>
@@ -652,23 +656,32 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>21</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -681,7 +694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>24</v>
       </c>
@@ -690,7 +703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>25</v>
       </c>
@@ -698,7 +711,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>26</v>
       </c>
@@ -706,7 +719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -715,7 +728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>24</v>
       </c>
@@ -723,7 +736,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>28</v>
       </c>
@@ -731,7 +744,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>29</v>
       </c>
@@ -739,7 +752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -748,12 +761,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>5</v>
       </c>
